--- a/public/templates/item_sampleFile.xlsx
+++ b/public/templates/item_sampleFile.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Category Name</t>
   </si>
@@ -65,25 +65,103 @@
     <t>Mobile Price</t>
   </si>
   <si>
+    <t>Addon Item Name</t>
+  </si>
+  <si>
+    <t>Addon POS Price</t>
+  </si>
+  <si>
+    <t>Addon Web Price</t>
+  </si>
+  <si>
+    <t>Addon Mobile Price</t>
+  </si>
+  <si>
+    <t>Addon Category Name</t>
+  </si>
+  <si>
+    <t>Addon Sub Category Name</t>
+  </si>
+  <si>
+    <t>Addon Description</t>
+  </si>
+  <si>
+    <t>Burgers</t>
+  </si>
+  <si>
+    <t>Veg Burgers</t>
+  </si>
+  <si>
+    <t>Aloo Tikki Burger</t>
+  </si>
+  <si>
+    <t>Crispy potato patty burger</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Cheese Slice|Extra Mayo</t>
+  </si>
+  <si>
+    <t>Addons</t>
+  </si>
+  <si>
+    <t>Burger Addons</t>
+  </si>
+  <si>
+    <t>Fresh cheese|Creamy mayo</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Veg Pizza</t>
+  </si>
+  <si>
+    <t>Margherita</t>
+  </si>
+  <si>
+    <t>Classic cheese pizza</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Extra Cheese|Olives|Jalapeno</t>
+  </si>
+  <si>
+    <t>Pizza Addons</t>
+  </si>
+  <si>
+    <t>Mozzarella|Sliced olives|Spicy jalapeno</t>
+  </si>
+  <si>
     <t>Beverages</t>
   </si>
   <si>
-    <t>Shakes</t>
-  </si>
-  <si>
-    <t>Chocolate Shake</t>
-  </si>
-  <si>
-    <t>Tasty</t>
-  </si>
-  <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XL </t>
+    <t>Cold Drinks</t>
+  </si>
+  <si>
+    <t>Lemon Soda</t>
+  </si>
+  <si>
+    <t>Refreshing soda</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Extra Ice</t>
+  </si>
+  <si>
+    <t>Drink Addons</t>
+  </si>
+  <si>
+    <t>Chilled ice</t>
   </si>
 </sst>
 </file>
@@ -446,33 +524,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19296F26-8260-413F-A2ED-D90CAFCDFFD6}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -500,93 +556,226 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="15">
+    <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="H2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I2">
-        <v>120</v>
+        <v>99</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15">
+    <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="H3">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I3">
-        <v>150</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H4">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="I4">
-        <v>160</v>
+        <v>199</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>40</v>
+      </c>
+      <c r="L4">
+        <v>40</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>49</v>
+      </c>
+      <c r="I5">
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
